--- a/使用说明/茗伊团队气劲面板命令.xlsx
+++ b/使用说明/茗伊团队气劲面板命令.xlsx
@@ -1,25 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23426"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\010\剑网3\工具代码\剑三插件数据解析\使用说明\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41F43050-B014-4AE1-9F98-505D01ADEA11}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队气劲面板命令" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -27,6 +18,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -34,279 +27,236 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="71">
+  <si>
+    <t>命令</t>
+  </si>
+  <si>
+    <t>参数</t>
+  </si>
+  <si>
+    <t>帮助，茗伊团队气劲面板指令版本，需要版本≥4.71，旧版本仅支持分析玩家技能与吃鸡地图</t>
+  </si>
   <si>
     <t>/szName</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>命令</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1个，字符串</t>
   </si>
   <si>
     <t>指定气劲自定义名称，如"/szName 减伤·春泥护花"，将气劲显示名称修改为 减伤·春泥护花</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>/nIcon</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1个，整数型</t>
   </si>
   <si>
     <t>指定气劲自定义图标，如"/nIcon 112"，将气劲图标自定义为112号图标</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>/MapID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无限，整数型，用逗号分割</t>
+  </si>
+  <si>
+    <t>指定气劲生效地图，如"/MapID -1,2"，将气劲生效地图设置为 通用地图（-1），万花地图（2）</t>
   </si>
   <si>
     <t>/nLevel</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定气劲等级，如"/nScrutinyType 2"，气劲等级为3，但不会勾选区分等级</t>
   </si>
   <si>
     <t>/nCount</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>指定气劲生效层数，如"/nCount 2"，气劲层数至少为2层才会触发</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>/nScrutinyType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>指定气劲等级，如"/nScrutinyType 2"，气劲等级为3，但不会勾选区分等级</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1个，整数型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1个，字符串</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>指定气劲监控对象，1自身，2团队，3敌对，4当前目标，如"/nScrutinyType 1"，气劲在自身生效才会触发</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>/tKungFu</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无限，字符串，用逗号分割</t>
+  </si>
+  <si>
+    <t>指定气劲生效心法，如"/tKungFu ["SKILL#10002"]=true,["SKILL#10003"]=true,"，洗髓经，易筋经，心法下生效</t>
   </si>
   <si>
     <t>/tMark</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10个，字符串，用逗号分割</t>
+  </si>
+  <si>
+    <t>指定气劲获得后标记，如"/tMark true,false,false,false,false,false,false,false,false,false"，获得气劲后标记为白云</t>
   </si>
   <si>
     <t>/disableTeamPanel</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>0个</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>指定气劲禁用团队面板，如"/disableTeamPanel"，此气劲不生效团队面板</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>/bCenterAlarm1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>指定气劲获得后中央警报，如"/bCenterAlarm1"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>/bCenterAlarm2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>指定气劲失去后中央警报，如"/bCenterAlarm2"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>/bPartyBuffList1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定气劲获得后团队气劲列表，如"/bPartyBuffList1"，获得气劲后显示团队气劲列表</t>
   </si>
   <si>
     <t>/bBuffList1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>指定气劲获得后自身气劲列表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>/szVoice1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定气劲获得后播放语音，如"/szVoice1 ZhuanHuo_T_BY"，获得气劲后播放 转火白云</t>
   </si>
   <si>
     <t>/szVoice2</t>
   </si>
   <si>
+    <t>指定气劲失去后播放语音，如"/szVoice1 ZhuanHuo_T_BY"，失去气劲后播放 转火白云</t>
+  </si>
+  <si>
     <t>/bVoiceSelfOnly1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定气劲获得后是否仅在自身气劲下播放语音</t>
   </si>
   <si>
     <t>/bVoiceSelfOnly2</t>
   </si>
   <si>
-    <t>指定气劲获得后是否仅在自身气劲下播放语音</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>指定气劲失去后是否仅在自身气劲下播放语音</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>/bTeamChannel1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定气劲获得后团队频道报警</t>
   </si>
   <si>
     <t>/bTeamChannel2</t>
   </si>
   <si>
+    <t>指定气劲失去后团队频道报警</t>
+  </si>
+  <si>
     <t>/bWhisperChannel1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定气劲获得后密聊频道报警</t>
   </si>
   <si>
     <t>/bWhisperChannel2</t>
   </si>
   <si>
-    <t>指定气劲获得后团队频道报警</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>指定气劲获得后密聊频道报警</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>指定气劲失去后团队频道报警</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>指定气劲失去后密聊频道报警</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>指定气劲获得后团队气劲列表，如"/bPartyBuffList1"，获得气劲后显示团队气劲列表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>指定气劲获得后播放语音，如"/szVoice1 ZhuanHuo_T_BY"，获得气劲后播放 转火白云</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>指定气劲失去后播放语音，如"/szVoice1 ZhuanHuo_T_BY"，失去气劲后播放 转火白云</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10个，字符串，用逗号分割</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>无限，字符串，用逗号分割</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>指定气劲获得后标记，如"/tMark true,false,false,false,false,false,false,false,false,false"，获得气劲后标记为白云</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>指定气劲生效心法，如"/tKungFu ["SKILL#10002"]=true,["SKILL#10003"]=true,"，洗髓经，易筋经，心法下生效</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>无限，整数型，用逗号分割</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>指定气劲生效地图，如"/MapID -1,2"，将气劲生效地图设置为 通用地图（-1），万花地图（2）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>帮助，茗伊团队气劲面板指令版本，需要版本≥4.71，旧版本仅支持分析玩家技能与吃鸡地图</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/reservedEx</t>
   </si>
   <si>
     <t>1个</t>
   </si>
   <si>
-    <t>/reservedEx</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>4.82新增。保留扩展，字符串直接拼接至原始数据</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>/shield</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.91优化。指定气劲在秘境地图不开启头顶染色，该指令只在气劲开启头顶警报功能且生效地图包含id为-1通用地图时有效</t>
   </si>
   <si>
     <t>/Reshield</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>4.91新增。与（/shield）指令相反，若该气劲在秘境地图屏蔽了头顶警报功能，则取消屏蔽，在秘境地图仍允许头顶染色</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.91优化。指定气劲在秘境地图不开启头顶染色，该指令只在气劲开启头顶警报功能且生效地图包含id为-1通用地图时有效</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/bTeamPanel</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5.11新增。参数为0则关闭仅显示来源自己的气劲（bOnlySelfSrc），大于0则开启。该指令指定气劲获得后团队面板，注：此指令操作的是动态事件的团队面板，而非条件团队面板，优点是可以设置监控对象（全部，自己）或是自身心法，缺点是无法设置备注文字与优先级</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/bFullScreen</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5.11新增。指定气劲获得后全屏泛光报警。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/bTeamPanel1</t>
+  </si>
+  <si>
+    <t>5.11新增。2026.10.11修改为/bTeamPanel1。参数为0则关闭仅显示来源自己的气劲（bOnlySelfSrc），大于0则开启。该指令指定气劲获得后团队面板，注：此指令操作的是动态事件的团队面板，而非条件团队面板，优点是可以设置监控对象（全部，自己）或是自身心法，缺点是无法设置备注文字与优先级</t>
+  </si>
+  <si>
+    <t>/bFullScreen1</t>
+  </si>
+  <si>
+    <t>5.11新增。2026.10.11修改为/bFullScreen1。指定气劲获得后全屏泛光报警。</t>
   </si>
   <si>
     <t>/col</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>3个，整数型，用逗号分割</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>2025.08.26新增。强制指定气劲通用颜色col的rgb值。例如"255,204,32,"最好尾部额外带一个逗号，防止Excel将其当做数值而非文本</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/bScreenHead1</t>
+  </si>
+  <si>
+    <t>2026.10.11新增。指定获得气劲开启头顶警报</t>
+  </si>
+  <si>
+    <t>/bVoiceOfficial1</t>
+  </si>
+  <si>
+    <t>2026.10.11新增。指定获得气劲优先使用官方语音条目</t>
+  </si>
+  <si>
+    <t>/bVoiceOfficial2</t>
+  </si>
+  <si>
+    <t>2026.10.11新增。指定失去气劲优先使用官方语音条目</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -314,11 +264,154 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -331,8 +424,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -342,22 +621,22 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right/>
       <top/>
@@ -366,10 +645,10 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top/>
       <bottom/>
@@ -377,42 +656,328 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -461,7 +1026,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
@@ -496,7 +1061,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
@@ -670,19 +1235,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="20.375" customWidth="1"/>
     <col min="2" max="2" width="39.875" customWidth="1"/>
@@ -690,306 +1250,306 @@
     <col min="4" max="4" width="40.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="3"/>
+      <c r="E1" s="4"/>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="3"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3">
       <c r="A24" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C24" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3">
       <c r="A26" s="5" t="s">
         <v>58</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3">
       <c r="A27" s="7" t="s">
         <v>60</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3">
       <c r="A28" s="7" t="s">
         <v>62</v>
       </c>
@@ -1000,9 +1560,42 @@
         <v>64</v>
       </c>
     </row>
+    <row r="29" customFormat="1" spans="1:3">
+      <c r="A29" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="30" customFormat="1" spans="1:3">
+      <c r="A30" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="31" customFormat="1" spans="1:3">
+      <c r="A31" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+  <headerFooter/>
 </worksheet>
 </file>